--- a/SLR/Full-Paper-Read/Paper-Review/PS19.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS19.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -26,48 +26,53 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>we report on our experience in developing the AMASS open source ecosystem. This ecosystem includes (1) an open source tool platform that supports the main CPS assurance and certification activities, (2) external tools with added-value features, and (3) an open community of developers and users. The platform integrates existing solutions for system modelling, process engineering, and compliance and argumentation management. We also present the application of the AMASS tool platform in 11 industrial case studies from five different application domains. The results show that the platform is a feasible means for CPS assurance and certification and that practitioners find benefits in assurance-oriented system modelling and in integrated system assurance information, among other areas. Nonetheless, improvement opportunities also exist, most notably regarding tool interoperability and usability.</t>
-  </si>
-  <si>
-    <t>I guess we should also include this paper in related work somehow?
-Also, we can probably get inspired from their related work section
-Worth highlighting being based on Eclipse</t>
+    <t>Paper discusses stakeholder collaboration in Digital Twin (DT) ecosystems. The paper is a SLR supplemented with data from interviews with industrial pracitioners from a research project (where 2 case studies have been implemented). The research objectives are: Empirically study stakeholder collaboration and challenges in dt ecosystems, explore state of the art, understand challenge and possible solutions at eco-system level. Three opportunites are found in this context (1) Dynamic DTs (2) Low code development (3) Data centric development. 8 experts interviewd. 10 papers are primary studies in DT ecosystems context. In both case studies stakeholder collaboration was important. Authors suggest standards as a means of adressing challenges, Also data encryption and blockchain for security.</t>
+  </si>
+  <si>
+    <t>Study originates from the Oxilate project. Since they find few studies in their context it can perhaps give some confidence that our number of studies identified are reasonable?
+2nd Reviewer: I agree, we can use it to motivate the number of papers selected in the SLR</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
-    <t>&gt;5</t>
-  </si>
-  <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>They describe two uses cases from a project</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Interoperability, cybersecurity, data governence and managemnet, data sharing and fusion, orchestration, stakeholder comitment, DT expertise</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>assurance and certification processes</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t xml:space="preserve">the ecosystem has been developed in the scope of a research project between industry and academia, including potential users of the AMASS tool platform. </t>
+    <t>N</t>
+  </si>
+  <si>
+    <t>They argue the paper can be used for future research, but do not draw any specific arguments for industry and academia collaboration.</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ2?</t>
@@ -76,25 +81,16 @@
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Automotive</t>
-  </si>
-  <si>
-    <t>Aerospace</t>
-  </si>
-  <si>
-    <t>Railway</t>
-  </si>
-  <si>
-    <t>Digital Life</t>
-  </si>
-  <si>
-    <t>Application Domain Independent</t>
-  </si>
-  <si>
-    <t>Avionics, Digital Automation</t>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Both case studies regard manufcaturing digital twin ecosystems</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
+  </si>
+  <si>
+    <t>This paper does several things, SLR + interview study</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -458,13 +454,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -472,11 +466,13 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -570,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -584,7 +580,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -599,35 +595,50 @@
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -672,10 +683,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -700,6 +711,9 @@
     </xf>
     <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -951,8 +965,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.5"/>
-    <col customWidth="1" min="2" max="2" width="45.13"/>
+    <col customWidth="1" min="1" max="1" width="2.25"/>
+    <col customWidth="1" min="2" max="2" width="51.38"/>
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
     <col customWidth="1" min="5" max="5" width="9.0"/>
@@ -999,7 +1013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="157.5" customHeight="1">
+    <row r="3" ht="147.0" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1017,8 +1031,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>7</v>
+      <c r="C4" s="17">
+        <v>2.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1026,7 +1040,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1034,18 +1048,18 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="19" t="s">
-        <v>8</v>
+      <c r="I5" s="21" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1059,21 +1073,21 @@
         <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1084,35 +1098,35 @@
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
+      <c r="C7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="21" t="s">
-        <v>8</v>
+      <c r="I7" s="26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="B8" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="21" t="s">
-        <v>17</v>
+      <c r="I8" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1120,18 +1134,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="19" t="s">
-        <v>8</v>
+      <c r="I9" s="30" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1139,28 +1153,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="C10" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="D10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>23</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1168,30 +1182,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="28">
+        <v>24</v>
+      </c>
+      <c r="C11" s="33">
         <f>Quality!C29</f>
-        <v>9.62962963</v>
-      </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="19" t="s">
-        <v>8</v>
+        <v>8.518518519</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="34" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="29" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2250,362 +2264,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="39"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="35" t="s">
+      <c r="B2" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="C2" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="43"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="44"/>
+      <c r="B3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C3" s="42">
         <v>1.0</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="38"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="36" t="s">
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="44"/>
+      <c r="B4" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C4" s="42">
         <v>1.0</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="38"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="39"/>
-      <c r="B4" s="36" t="s">
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="44"/>
+      <c r="B5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C5" s="42">
         <v>1.0</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="36" t="s">
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44"/>
+      <c r="B6" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C6" s="42">
         <v>1.0</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="39"/>
-      <c r="B6" s="36" t="s">
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="45"/>
+      <c r="B7" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C7" s="42">
         <v>1.0</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="40"/>
-      <c r="B7" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="37">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="41">
+      <c r="D7" s="46">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="46">
         <f>(SUM(C2:C7)/D7)*10</f>
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="C8" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="44"/>
+      <c r="B9" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C9" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="44"/>
+      <c r="B10" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="50">
         <v>1.0</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="39"/>
-      <c r="B9" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="44">
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="44"/>
+      <c r="B11" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="49">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="44"/>
+      <c r="B12" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="49">
         <v>1.0</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="39"/>
-      <c r="B10" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="44">
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44"/>
+      <c r="B13" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="50">
         <v>1.0</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="39"/>
-      <c r="B11" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="44">
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44"/>
+      <c r="B14" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="50">
         <v>1.0</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="39"/>
-      <c r="B12" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="45">
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44"/>
+      <c r="B15" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44"/>
+      <c r="B16" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44"/>
+      <c r="B17" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44"/>
+      <c r="B18" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45"/>
+      <c r="B19" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="49">
         <v>0.5</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="39"/>
-      <c r="B13" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="39"/>
-      <c r="B14" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="39"/>
-      <c r="B15" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="39"/>
-      <c r="B16" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="39"/>
-      <c r="B17" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="39"/>
-      <c r="B18" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="40"/>
-      <c r="B19" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="41">
+      <c r="D19" s="46">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="46">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>9.583333333</v>
+        <v>7.916666667</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="C20" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44"/>
+      <c r="B21" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="48">
+      <c r="C21" s="54">
         <v>1.0</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="39"/>
-      <c r="B21" s="47" t="s">
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44"/>
+      <c r="B22" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C22" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44"/>
+      <c r="B23" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="54">
         <v>1.0</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="39"/>
-      <c r="B22" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="48">
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="43"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44"/>
+      <c r="B24" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="53">
         <v>1.0</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39"/>
-      <c r="B23" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="38"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39"/>
-      <c r="B24" s="47" t="s">
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="43"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="45"/>
+      <c r="B25" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="48">
+      <c r="C25" s="53">
         <v>1.0</v>
       </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="38"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="40"/>
-      <c r="B25" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="50">
+      <c r="D25" s="55">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="55">
         <f>(SUM(C20:C25)/D25)*10</f>
         <v>9.166666667</v>
       </c>
-      <c r="F25" s="38"/>
+      <c r="F25" s="43"/>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="C26" s="58">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="43"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44"/>
+      <c r="B27" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C27" s="58">
         <v>1.0</v>
       </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="38"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="39"/>
-      <c r="B27" s="52" t="s">
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="43"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="45"/>
+      <c r="B28" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="38"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="40"/>
-      <c r="B28" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="50">
+      <c r="C28" s="59">
+        <v>0.0</v>
+      </c>
+      <c r="D28" s="55">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="55">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F28" s="38"/>
+        <v>6.666666667</v>
+      </c>
+      <c r="F28" s="43"/>
     </row>
     <row r="29">
-      <c r="B29" s="54">
+      <c r="B29" s="60">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="60">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>9.62962963</v>
+        <v>8.518518519</v>
       </c>
     </row>
   </sheetData>
